--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T09:14:32+00:00</t>
+    <t>2026-03-01T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -43,7 +43,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>WHOQOL-BREF Answer Scales</t>
+    <t>AT PreNUDGE WHOQOL-BREF Answer Scales</t>
   </si>
   <si>
     <t>Status</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="115">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -307,6 +307,9 @@
     <t>C3</t>
   </si>
   <si>
+    <t>Halbwegs</t>
+  </si>
+  <si>
     <t>C4</t>
   </si>
   <si>
@@ -337,19 +340,19 @@
     <t>F2</t>
   </si>
   <si>
-    <t>Selten</t>
+    <t>Nicht oft</t>
   </si>
   <si>
     <t>F3</t>
   </si>
   <si>
-    <t>Ziemlich oft</t>
+    <t>Zeitweilig</t>
   </si>
   <si>
     <t>F4</t>
   </si>
   <si>
-    <t>Sehr oft</t>
+    <t>Oftmals</t>
   </si>
   <si>
     <t>F5</t>
@@ -1006,7 +1009,7 @@
         <v>96</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -1015,10 +1018,10 @@
         <v>54</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -1027,10 +1030,10 @@
         <v>54</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -1039,13 +1042,13 @@
         <v>50</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27">
@@ -1053,10 +1056,10 @@
         <v>54</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -1065,10 +1068,10 @@
         <v>54</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -1077,10 +1080,10 @@
         <v>54</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -1089,10 +1092,10 @@
         <v>54</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" s="2"/>
     </row>
@@ -1101,10 +1104,10 @@
         <v>54</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D31" s="2"/>
     </row>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/CodeSystem-whoqol-bref-scale.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
